--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T12:42:43+00:00</t>
+    <t>2026-06-22T14:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -485,7 +485,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant. L'entrée Traitement doit être identifiée de manière unique.</t>
+    <t>External identifier</t>
   </si>
   <si>
     <t>Identifiers associated with this Medication Statement that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:38:01+00:00</t>
+    <t>2026-06-29T12:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:42:10+00:00</t>
+    <t>2026-07-07T09:34:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1141,7 +1141,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-human-substance-administration-site-cisis|20260420150249</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-human-substance-administration-site-cisis|20260619134041</t>
   </si>
   <si>
     <t>Dosage.site</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T09:34:50+00:00</t>
+    <t>2026-07-16T11:52:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T11:52:18+00:00</t>
+    <t>2026-07-16T13:43:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T13:43:45+00:00</t>
+    <t>2026-07-16T16:12:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T16:12:39+00:00</t>
+    <t>2026-07-20T14:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4619,7 +4619,7 @@
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>78</v>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:23:22+00:00</t>
+    <t>2026-08-12T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -844,7 +844,7 @@
 </t>
   </si>
   <si>
-    <t>Conditions préalables à l'utilisation du médicament.</t>
+    <t>Further information about the statement</t>
   </si>
   <si>
     <t>Provides extra information about the medication statement that is not conveyed by the other attributes.</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T15:16:17+00:00</t>
+    <t>2026-08-13T08:08:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T08:08:00+00:00</t>
+    <t>2026-08-13T08:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T08:33:40+00:00</t>
+    <t>2026-08-13T08:58:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T08:58:16+00:00</t>
+    <t>2026-08-13T09:15:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:15:12+00:00</t>
+    <t>2026-08-13T09:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:41:50+00:00</t>
+    <t>2026-08-13T12:00:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T12:00:16+00:00</t>
+    <t>2026-08-13T12:31:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
